--- a/docs/Пример спецификации.xlsx
+++ b/docs/Пример спецификации.xlsx
@@ -8,7 +8,8 @@
   <x:sheets>
     <x:sheet name="Спецификация" sheetId="1" r:id="rId2"/>
     <x:sheet name="Основная надпись" sheetId="2" r:id="rId3"/>
-    <x:sheet name="Как заполнять" sheetId="3" r:id="rId4"/>
+    <x:sheet name="Изменения" sheetId="3" r:id="rId4"/>
+    <x:sheet name="Как заполнять" sheetId="4" r:id="rId5"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="_xlnm.Print_Titles" localSheetId="0">Спецификация!1:1</x:definedName>
@@ -194,6 +195,39 @@
     <x:t>Перв. примен.</x:t>
   </x:si>
   <x:si>
+    <x:t>Изм.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Кол. уч.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Лист</x:t>
+  </x:si>
+  <x:si>
+    <x:t>№ докум.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Подп.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Дата</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>АБВГ.12-25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Петров</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.25</x:t>
+  </x:si>
+  <x:si>
     <x:t>Как заполнять</x:t>
   </x:si>
   <x:si>
@@ -225,6 +259,21 @@
   </x:si>
   <x:si>
     <x:t>Лист «Основная надпись» — данные для основной надписи (обозначение, наименование, подписи).</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Лист «Изменения» — графы изменений основной надписи (ГОСТ 2.503), одна строка — одна запись, по порядку внесения:</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">  Изм. — порядковый номер изменения; Кол. уч. — количество изменённых участков на листе;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">  Лист — номер изменённого листа; № докум. — обозначение извещения об изменении; Подп. и Дата — кто и когда внёс.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>При выводе в PDF запись попадает в основную надпись указанного листа (пустой «Лист» — первый лист);</x:t>
+  </x:si>
+  <x:si>
+    <x:t>если записей больше, чем граф в основной надписи, выводятся последние. Ячейки — текстовые, вводите как есть.</x:t>
   </x:si>
   <x:si>
     <x:t>Файл создан аддином InventorGostSpec. Изменения в нём не возвращаются в сборку Inventor.</x:t>
@@ -234,9 +283,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="2">
+  <x:numFmts count="3">
     <x:numFmt numFmtId="0" formatCode=""/>
     <x:numFmt numFmtId="164" formatCode="0.###"/>
+    <x:numFmt numFmtId="165" formatCode="@"/>
   </x:numFmts>
   <x:fonts count="6">
     <x:font>
@@ -346,7 +396,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="11">
+  <x:cellStyleXfs count="12">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -377,11 +427,14 @@
     <x:xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="18">
+  <x:cellXfs count="20">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -448,6 +501,14 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -1418,15 +1479,160 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:A15"/>
+  <x:dimension ref="A1:F12"/>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="7.710625" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="9.710625" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="12.710625" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="24.710625" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18.710625" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="12.710625" style="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" spans="1:6">
+      <x:c r="A1" s="17" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B1" s="17" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C1" s="17" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="D1" s="17" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E1" s="17" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="F1" s="17" t="s">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:6">
+      <x:c r="A2" s="18" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B2" s="18" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C2" s="18" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="D2" s="18" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E2" s="18" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="F2" s="18" t="s">
+        <x:v>68</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:6">
+      <x:c r="A3" s="18"/>
+      <x:c r="B3" s="18"/>
+      <x:c r="C3" s="18"/>
+      <x:c r="D3" s="18"/>
+      <x:c r="E3" s="18"/>
+      <x:c r="F3" s="18"/>
+    </x:row>
+    <x:row r="4" spans="1:6">
+      <x:c r="A4" s="18"/>
+      <x:c r="B4" s="18"/>
+      <x:c r="C4" s="18"/>
+      <x:c r="D4" s="18"/>
+      <x:c r="E4" s="18"/>
+      <x:c r="F4" s="18"/>
+    </x:row>
+    <x:row r="5" spans="1:6">
+      <x:c r="A5" s="18"/>
+      <x:c r="B5" s="18"/>
+      <x:c r="C5" s="18"/>
+      <x:c r="D5" s="18"/>
+      <x:c r="E5" s="18"/>
+      <x:c r="F5" s="18"/>
+    </x:row>
+    <x:row r="6" spans="1:6">
+      <x:c r="A6" s="18"/>
+      <x:c r="B6" s="18"/>
+      <x:c r="C6" s="18"/>
+      <x:c r="D6" s="18"/>
+      <x:c r="E6" s="18"/>
+      <x:c r="F6" s="18"/>
+    </x:row>
+    <x:row r="7" spans="1:6">
+      <x:c r="A7" s="18"/>
+      <x:c r="B7" s="18"/>
+      <x:c r="C7" s="18"/>
+      <x:c r="D7" s="18"/>
+      <x:c r="E7" s="18"/>
+      <x:c r="F7" s="18"/>
+    </x:row>
+    <x:row r="8" spans="1:6">
+      <x:c r="A8" s="18"/>
+      <x:c r="B8" s="18"/>
+      <x:c r="C8" s="18"/>
+      <x:c r="D8" s="18"/>
+      <x:c r="E8" s="18"/>
+      <x:c r="F8" s="18"/>
+    </x:row>
+    <x:row r="9" spans="1:6">
+      <x:c r="A9" s="18"/>
+      <x:c r="B9" s="18"/>
+      <x:c r="C9" s="18"/>
+      <x:c r="D9" s="18"/>
+      <x:c r="E9" s="18"/>
+      <x:c r="F9" s="18"/>
+    </x:row>
+    <x:row r="10" spans="1:6">
+      <x:c r="A10" s="18"/>
+      <x:c r="B10" s="18"/>
+      <x:c r="C10" s="18"/>
+      <x:c r="D10" s="18"/>
+      <x:c r="E10" s="18"/>
+      <x:c r="F10" s="18"/>
+    </x:row>
+    <x:row r="11" spans="1:6">
+      <x:c r="A11" s="18"/>
+      <x:c r="B11" s="18"/>
+      <x:c r="C11" s="18"/>
+      <x:c r="D11" s="18"/>
+      <x:c r="E11" s="18"/>
+      <x:c r="F11" s="18"/>
+    </x:row>
+    <x:row r="12" spans="1:6">
+      <x:c r="A12" s="18"/>
+      <x:c r="B12" s="18"/>
+      <x:c r="C12" s="18"/>
+      <x:c r="D12" s="18"/>
+      <x:c r="E12" s="18"/>
+      <x:c r="F12" s="18"/>
+    </x:row>
+  </x:sheetData>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter/>
+  <x:tableParts count="0"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="1" summaryRight="1"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:A21"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="120.710625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:1">
-      <x:c r="A1" s="17" t="s">
-        <x:v>58</x:v>
+      <x:c r="A1" s="19" t="s">
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:1">
@@ -1436,47 +1642,47 @@
     </x:row>
     <x:row r="3" spans="1:1">
       <x:c r="A3" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:1">
       <x:c r="A4" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:1">
       <x:c r="A5" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:1">
       <x:c r="A6" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:1">
       <x:c r="A7" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:1">
       <x:c r="A8" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:1">
       <x:c r="A9" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:1">
       <x:c r="A10" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:1">
       <x:c r="A11" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:1">
@@ -1486,7 +1692,7 @@
     </x:row>
     <x:row r="13" spans="1:1">
       <x:c r="A13" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:1">
@@ -1496,7 +1702,37 @@
     </x:row>
     <x:row r="15" spans="1:1">
       <x:c r="A15" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:1">
+      <x:c r="A16" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:1">
+      <x:c r="A17" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:1">
+      <x:c r="A18" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:1">
+      <x:c r="A19" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:1">
+      <x:c r="A20" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:1">
+      <x:c r="A21" s="0" t="s">
+        <x:v>85</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/docs/Пример спецификации.xlsx
+++ b/docs/Пример спецификации.xlsx
@@ -195,6 +195,9 @@
     <x:t>Перв. примен.</x:t>
   </x:si>
   <x:si>
+    <x:t>Шрифт наименования, мм</x:t>
+  </x:si>
+  <x:si>
     <x:t>Изм.</x:t>
   </x:si>
   <x:si>
@@ -249,18 +252,45 @@
     <x:t xml:space="preserve">  Текст — строка текста без позиции (в «Наименовании»);</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">  Резерв — пустая строка резервной позиции (номер позиции можно оставить или стереть).</x:t>
+    <x:t xml:space="preserve">  Резерв — свободная строка резервной позиции (номер позиции для справки, в PDF не выводится);</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">  Пустая — пустая строка, добавленная вручную: например, чтобы сдвинуть запись на следующий лист;</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">  Новый лист — следующие строки начинаются с нового листа PDF (сама строка не выводится).</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Колонка «Лист PDF» и жирные линии показывают, где кончается лист PDF. После ручной правки обновите разметку</x:t>
+  </x:si>
+  <x:si>
+    <x:t>кнопкой «Разметить листы в Excel» в утилите PDF (файл Excel должен быть закрыт).</x:t>
   </x:si>
   <x:si>
     <x:t>Пустой «Тип строки» у заполненной строки считается «Изделием», у пустой — пустой строкой.</x:t>
   </x:si>
   <x:si>
+    <x:t>Ручной перенос строки — Alt+Enter внутри ячейки: в PDF текст перенесётся в этом месте (Обозначение, Наименование,</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Примечание; на листе «Основная надпись» — Наименование и Организация). Без него длинный текст сжимается</x:t>
+  </x:si>
+  <x:si>
+    <x:t>до 80 % по ширине, а если не помещается и так — переносится по словам.</x:t>
+  </x:si>
+  <x:si>
     <x:t>«Ед. изм.» выводится вместе с количеством (например, «2,5 м»); для штук оставьте пустым.</x:t>
   </x:si>
   <x:si>
     <x:t>Лист «Основная надпись» — данные для основной надписи (обозначение, наименование, подписи).</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">  «Шрифт наименования, мм» — высота шрифта наименования изделия в основной надписи (2,5; 3,5; 5; 7; 10).</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">  Не помещается — сжимается по ширине и переносится. Организация выводится шрифтом 10 одной строкой.</x:t>
+  </x:si>
+  <x:si>
     <x:t>Лист «Изменения» — графы изменений основной надписи (ГОСТ 2.503), одна строка — одна запись, по порядку внесения:</x:t>
   </x:si>
   <x:si>
@@ -270,25 +300,29 @@
     <x:t xml:space="preserve">  Лист — номер изменённого листа; № докум. — обозначение извещения об изменении; Подп. и Дата — кто и когда внёс.</x:t>
   </x:si>
   <x:si>
-    <x:t>При выводе в PDF запись попадает в основную надпись указанного листа (пустой «Лист» — первый лист);</x:t>
+    <x:t>При выводе в PDF все записи попадают в основную надпись первого листа, а также указанного в «Лист» листа;</x:t>
   </x:si>
   <x:si>
     <x:t>если записей больше, чем граф в основной надписи, выводятся последние. Ячейки — текстовые, вводите как есть.</x:t>
   </x:si>
   <x:si>
     <x:t>Файл создан аддином InventorGostSpec. Изменения в нём не возвращаются в сборку Inventor.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Лист PDF</x:t>
   </x:si>
 </x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="3">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="0" formatCode=""/>
     <x:numFmt numFmtId="164" formatCode="0.###"/>
-    <x:numFmt numFmtId="165" formatCode="@"/>
+    <x:numFmt numFmtId="165" formatCode="0.#"/>
+    <x:numFmt numFmtId="166" formatCode="@"/>
   </x:numFmts>
-  <x:fonts count="6">
+  <x:fonts count="7">
     <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="11"/>
@@ -336,6 +370,14 @@
       <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="11"/>
+      <x:color rgb="FF1F2937"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
   </x:fonts>
   <x:fills count="5">
     <x:fill>
@@ -360,7 +402,7 @@
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="2">
+  <x:borders count="4">
     <x:border diagonalUp="0" diagonalDown="0">
       <x:left style="none">
         <x:color rgb="FF000000"/>
@@ -395,8 +437,42 @@
         <x:color rgb="FF000000"/>
       </x:diagonal>
     </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="thin">
+        <x:color rgb="FFD9DDE3"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD9DDE3"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD9DDE3"/>
+      </x:top>
+      <x:bottom style="thick">
+        <x:color rgb="FF1F2937"/>
+      </x:bottom>
+      <x:diagonal style="none">
+        <x:color rgb="FF000000"/>
+      </x:diagonal>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="none">
+        <x:color rgb="FF000000"/>
+      </x:left>
+      <x:right style="none">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="none">
+        <x:color rgb="FF000000"/>
+      </x:top>
+      <x:bottom style="thick">
+        <x:color rgb="FF1F2937"/>
+      </x:bottom>
+      <x:diagonal style="none">
+        <x:color rgb="FF000000"/>
+      </x:diagonal>
+    </x:border>
   </x:borders>
-  <x:cellStyleXfs count="12">
+  <x:cellStyleXfs count="19">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -430,11 +506,32 @@
     <x:xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="166" fontId="0" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="0" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="20">
+  <x:cellXfs count="28">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -503,15 +600,47 @@
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -822,9 +951,10 @@
     <x:col min="7" max="7" width="7.710625" style="1" customWidth="1"/>
     <x:col min="8" max="8" width="8.710625" style="1" customWidth="1"/>
     <x:col min="9" max="9" width="22.710625" style="0" customWidth="1"/>
+    <x:col min="10" max="10" width="9.710625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:9" ht="22" customHeight="1">
+    <x:row r="1" spans="1:10" ht="22" customHeight="1">
       <x:c r="A1" s="2" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -852,8 +982,11 @@
       <x:c r="I1" s="2" t="s">
         <x:v>8</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2" spans="1:9">
+      <x:c r="J1" s="21" t="s">
+        <x:v>96</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:10">
       <x:c r="A2" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
@@ -867,8 +1000,11 @@
       <x:c r="G2" s="4"/>
       <x:c r="H2" s="4"/>
       <x:c r="I2" s="5"/>
-    </x:row>
-    <x:row r="3" spans="1:9">
+      <x:c r="J2" s="22">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:10">
       <x:c r="A3" s="7" t="s">
         <x:v>11</x:v>
       </x:c>
@@ -895,7 +1031,7 @@
         <x:v>13</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" spans="1:9">
+    <x:row r="4" spans="1:10">
       <x:c r="A4" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
@@ -910,7 +1046,7 @@
       <x:c r="H4" s="4"/>
       <x:c r="I4" s="5"/>
     </x:row>
-    <x:row r="5" spans="1:9">
+    <x:row r="5" spans="1:10">
       <x:c r="A5" s="7" t="s">
         <x:v>11</x:v>
       </x:c>
@@ -939,7 +1075,7 @@
         <x:v>13</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" spans="1:9">
+    <x:row r="6" spans="1:10">
       <x:c r="A6" s="7" t="s">
         <x:v>11</x:v>
       </x:c>
@@ -968,7 +1104,7 @@
         <x:v>13</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" spans="1:9">
+    <x:row r="7" spans="1:10">
       <x:c r="A7" s="7" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -983,7 +1119,7 @@
       <x:c r="H7" s="11"/>
       <x:c r="I7" s="7"/>
     </x:row>
-    <x:row r="8" spans="1:9">
+    <x:row r="8" spans="1:10">
       <x:c r="A8" s="7" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -998,7 +1134,7 @@
       <x:c r="H8" s="11"/>
       <x:c r="I8" s="7"/>
     </x:row>
-    <x:row r="9" spans="1:9">
+    <x:row r="9" spans="1:10">
       <x:c r="A9" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
@@ -1013,7 +1149,7 @@
       <x:c r="H9" s="4"/>
       <x:c r="I9" s="5"/>
     </x:row>
-    <x:row r="10" spans="1:9">
+    <x:row r="10" spans="1:10">
       <x:c r="A10" s="7" t="s">
         <x:v>11</x:v>
       </x:c>
@@ -1042,7 +1178,7 @@
         <x:v>27</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:9">
+    <x:row r="11" spans="1:10">
       <x:c r="A11" s="7" t="s">
         <x:v>11</x:v>
       </x:c>
@@ -1071,7 +1207,7 @@
         <x:v>13</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:9">
+    <x:row r="12" spans="1:10">
       <x:c r="A12" s="7" t="s">
         <x:v>11</x:v>
       </x:c>
@@ -1100,7 +1236,7 @@
         <x:v>13</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:9">
+    <x:row r="13" spans="1:10">
       <x:c r="A13" s="7" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -1115,7 +1251,7 @@
       <x:c r="H13" s="11"/>
       <x:c r="I13" s="7"/>
     </x:row>
-    <x:row r="14" spans="1:9">
+    <x:row r="14" spans="1:10">
       <x:c r="A14" s="7" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -1130,7 +1266,7 @@
       <x:c r="H14" s="11"/>
       <x:c r="I14" s="7"/>
     </x:row>
-    <x:row r="15" spans="1:9">
+    <x:row r="15" spans="1:10">
       <x:c r="A15" s="7" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -1145,7 +1281,7 @@
       <x:c r="H15" s="11"/>
       <x:c r="I15" s="7"/>
     </x:row>
-    <x:row r="16" spans="1:9">
+    <x:row r="16" spans="1:10">
       <x:c r="A16" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
@@ -1160,7 +1296,7 @@
       <x:c r="H16" s="4"/>
       <x:c r="I16" s="5"/>
     </x:row>
-    <x:row r="17" spans="1:9">
+    <x:row r="17" spans="1:10">
       <x:c r="A17" s="7" t="s">
         <x:v>11</x:v>
       </x:c>
@@ -1189,7 +1325,7 @@
         <x:v>13</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:9">
+    <x:row r="18" spans="1:10">
       <x:c r="A18" s="7" t="s">
         <x:v>11</x:v>
       </x:c>
@@ -1218,36 +1354,37 @@
         <x:v>13</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:9">
-      <x:c r="A19" s="7" t="s">
+    <x:row r="19" spans="1:10">
+      <x:c r="A19" s="23" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B19" s="8" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C19" s="8" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D19" s="8">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E19" s="9" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F19" s="9" t="s">
+      <x:c r="B19" s="24" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C19" s="24" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D19" s="24">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E19" s="25" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F19" s="25" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="G19" s="10">
+      <x:c r="G19" s="26">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H19" s="8" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="I19" s="9" t="s">
-        <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:9">
+      <x:c r="H19" s="24" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="I19" s="25" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="J19" s="27"/>
+    </x:row>
+    <x:row r="20" spans="1:10">
       <x:c r="A20" s="12" t="s">
         <x:v>37</x:v>
       </x:c>
@@ -1261,8 +1398,11 @@
       <x:c r="G20" s="13"/>
       <x:c r="H20" s="13"/>
       <x:c r="I20" s="14"/>
-    </x:row>
-    <x:row r="21" spans="1:9">
+      <x:c r="J20" s="22">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:10">
       <x:c r="A21" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
@@ -1277,7 +1417,7 @@
       <x:c r="H21" s="4"/>
       <x:c r="I21" s="5"/>
     </x:row>
-    <x:row r="22" spans="1:9">
+    <x:row r="22" spans="1:10">
       <x:c r="A22" s="7" t="s">
         <x:v>11</x:v>
       </x:c>
@@ -1306,7 +1446,7 @@
         <x:v>13</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" spans="1:9">
+    <x:row r="23" spans="1:10">
       <x:c r="A23" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
@@ -1321,7 +1461,7 @@
       <x:c r="H23" s="4"/>
       <x:c r="I23" s="5"/>
     </x:row>
-    <x:row r="24" spans="1:9">
+    <x:row r="24" spans="1:10">
       <x:c r="A24" s="7" t="s">
         <x:v>11</x:v>
       </x:c>
@@ -1352,8 +1492,8 @@
     </x:row>
   </x:sheetData>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" errorStyle="stop" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Тип строки" error="Выберите тип из списка: Группа, Раздел, Изделие, Текст, Резерв." promptTitle="" prompt="" sqref="A2:A2000">
-      <x:formula1>"Группа,Раздел,Изделие,Текст,Резерв"</x:formula1>
+    <x:dataValidation type="list" errorStyle="stop" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Тип строки" error="Выберите тип из списка: Группа, Раздел, Изделие, Текст, Резерв, Пустая, Новый лист." promptTitle="" prompt="" sqref="A2:A2000">
+      <x:formula1>"Группа,Раздел,Изделие,Текст,Резерв,Пустая,Новый лист"</x:formula1>
       <x:formula2/>
     </x:dataValidation>
   </x:dataValidations>
@@ -1370,10 +1510,10 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:B11"/>
+  <x:dimension ref="A1:B12"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="18.710625" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="24.710625" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="60.710625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -1463,6 +1603,14 @@
       </x:c>
       <x:c r="B11" s="16" t="s">
         <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:2">
+      <x:c r="A12" s="16" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B12" s="17">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1491,124 +1639,124 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:6">
-      <x:c r="A1" s="17" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="B1" s="17" t="s">
+      <x:c r="A1" s="18" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="C1" s="17" t="s">
+      <x:c r="B1" s="18" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="D1" s="17" t="s">
+      <x:c r="C1" s="18" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="E1" s="17" t="s">
+      <x:c r="D1" s="18" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="F1" s="17" t="s">
+      <x:c r="E1" s="18" t="s">
         <x:v>63</x:v>
       </x:c>
+      <x:c r="F1" s="18" t="s">
+        <x:v>64</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" spans="1:6">
-      <x:c r="A2" s="18" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="B2" s="18" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C2" s="18" t="s">
+      <x:c r="A2" s="19" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="D2" s="18" t="s">
+      <x:c r="B2" s="19" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C2" s="19" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="E2" s="18" t="s">
+      <x:c r="D2" s="19" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="F2" s="18" t="s">
+      <x:c r="E2" s="19" t="s">
         <x:v>68</x:v>
       </x:c>
+      <x:c r="F2" s="19" t="s">
+        <x:v>69</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" spans="1:6">
-      <x:c r="A3" s="18"/>
-      <x:c r="B3" s="18"/>
-      <x:c r="C3" s="18"/>
-      <x:c r="D3" s="18"/>
-      <x:c r="E3" s="18"/>
-      <x:c r="F3" s="18"/>
+      <x:c r="A3" s="19"/>
+      <x:c r="B3" s="19"/>
+      <x:c r="C3" s="19"/>
+      <x:c r="D3" s="19"/>
+      <x:c r="E3" s="19"/>
+      <x:c r="F3" s="19"/>
     </x:row>
     <x:row r="4" spans="1:6">
-      <x:c r="A4" s="18"/>
-      <x:c r="B4" s="18"/>
-      <x:c r="C4" s="18"/>
-      <x:c r="D4" s="18"/>
-      <x:c r="E4" s="18"/>
-      <x:c r="F4" s="18"/>
+      <x:c r="A4" s="19"/>
+      <x:c r="B4" s="19"/>
+      <x:c r="C4" s="19"/>
+      <x:c r="D4" s="19"/>
+      <x:c r="E4" s="19"/>
+      <x:c r="F4" s="19"/>
     </x:row>
     <x:row r="5" spans="1:6">
-      <x:c r="A5" s="18"/>
-      <x:c r="B5" s="18"/>
-      <x:c r="C5" s="18"/>
-      <x:c r="D5" s="18"/>
-      <x:c r="E5" s="18"/>
-      <x:c r="F5" s="18"/>
+      <x:c r="A5" s="19"/>
+      <x:c r="B5" s="19"/>
+      <x:c r="C5" s="19"/>
+      <x:c r="D5" s="19"/>
+      <x:c r="E5" s="19"/>
+      <x:c r="F5" s="19"/>
     </x:row>
     <x:row r="6" spans="1:6">
-      <x:c r="A6" s="18"/>
-      <x:c r="B6" s="18"/>
-      <x:c r="C6" s="18"/>
-      <x:c r="D6" s="18"/>
-      <x:c r="E6" s="18"/>
-      <x:c r="F6" s="18"/>
+      <x:c r="A6" s="19"/>
+      <x:c r="B6" s="19"/>
+      <x:c r="C6" s="19"/>
+      <x:c r="D6" s="19"/>
+      <x:c r="E6" s="19"/>
+      <x:c r="F6" s="19"/>
     </x:row>
     <x:row r="7" spans="1:6">
-      <x:c r="A7" s="18"/>
-      <x:c r="B7" s="18"/>
-      <x:c r="C7" s="18"/>
-      <x:c r="D7" s="18"/>
-      <x:c r="E7" s="18"/>
-      <x:c r="F7" s="18"/>
+      <x:c r="A7" s="19"/>
+      <x:c r="B7" s="19"/>
+      <x:c r="C7" s="19"/>
+      <x:c r="D7" s="19"/>
+      <x:c r="E7" s="19"/>
+      <x:c r="F7" s="19"/>
     </x:row>
     <x:row r="8" spans="1:6">
-      <x:c r="A8" s="18"/>
-      <x:c r="B8" s="18"/>
-      <x:c r="C8" s="18"/>
-      <x:c r="D8" s="18"/>
-      <x:c r="E8" s="18"/>
-      <x:c r="F8" s="18"/>
+      <x:c r="A8" s="19"/>
+      <x:c r="B8" s="19"/>
+      <x:c r="C8" s="19"/>
+      <x:c r="D8" s="19"/>
+      <x:c r="E8" s="19"/>
+      <x:c r="F8" s="19"/>
     </x:row>
     <x:row r="9" spans="1:6">
-      <x:c r="A9" s="18"/>
-      <x:c r="B9" s="18"/>
-      <x:c r="C9" s="18"/>
-      <x:c r="D9" s="18"/>
-      <x:c r="E9" s="18"/>
-      <x:c r="F9" s="18"/>
+      <x:c r="A9" s="19"/>
+      <x:c r="B9" s="19"/>
+      <x:c r="C9" s="19"/>
+      <x:c r="D9" s="19"/>
+      <x:c r="E9" s="19"/>
+      <x:c r="F9" s="19"/>
     </x:row>
     <x:row r="10" spans="1:6">
-      <x:c r="A10" s="18"/>
-      <x:c r="B10" s="18"/>
-      <x:c r="C10" s="18"/>
-      <x:c r="D10" s="18"/>
-      <x:c r="E10" s="18"/>
-      <x:c r="F10" s="18"/>
+      <x:c r="A10" s="19"/>
+      <x:c r="B10" s="19"/>
+      <x:c r="C10" s="19"/>
+      <x:c r="D10" s="19"/>
+      <x:c r="E10" s="19"/>
+      <x:c r="F10" s="19"/>
     </x:row>
     <x:row r="11" spans="1:6">
-      <x:c r="A11" s="18"/>
-      <x:c r="B11" s="18"/>
-      <x:c r="C11" s="18"/>
-      <x:c r="D11" s="18"/>
-      <x:c r="E11" s="18"/>
-      <x:c r="F11" s="18"/>
+      <x:c r="A11" s="19"/>
+      <x:c r="B11" s="19"/>
+      <x:c r="C11" s="19"/>
+      <x:c r="D11" s="19"/>
+      <x:c r="E11" s="19"/>
+      <x:c r="F11" s="19"/>
     </x:row>
     <x:row r="12" spans="1:6">
-      <x:c r="A12" s="18"/>
-      <x:c r="B12" s="18"/>
-      <x:c r="C12" s="18"/>
-      <x:c r="D12" s="18"/>
-      <x:c r="E12" s="18"/>
-      <x:c r="F12" s="18"/>
+      <x:c r="A12" s="19"/>
+      <x:c r="B12" s="19"/>
+      <x:c r="C12" s="19"/>
+      <x:c r="D12" s="19"/>
+      <x:c r="E12" s="19"/>
+      <x:c r="F12" s="19"/>
     </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
@@ -1624,15 +1772,15 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:A21"/>
+  <x:dimension ref="A1:A30"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="120.710625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:1">
-      <x:c r="A1" s="19" t="s">
-        <x:v>69</x:v>
+      <x:c r="A1" s="20" t="s">
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:1">
@@ -1642,97 +1790,142 @@
     </x:row>
     <x:row r="3" spans="1:1">
       <x:c r="A3" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:1">
       <x:c r="A4" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:1">
       <x:c r="A5" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:1">
       <x:c r="A6" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:1">
       <x:c r="A7" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:1">
       <x:c r="A8" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:1">
       <x:c r="A9" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:1">
       <x:c r="A10" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:1">
       <x:c r="A11" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:1">
       <x:c r="A12" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:1">
       <x:c r="A13" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:1">
       <x:c r="A14" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:1">
       <x:c r="A15" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:1">
       <x:c r="A16" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:1">
       <x:c r="A17" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:1">
       <x:c r="A18" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:1">
       <x:c r="A19" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:1">
       <x:c r="A20" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:1">
       <x:c r="A21" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>88</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:1">
+      <x:c r="A22" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:1">
+      <x:c r="A23" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:1">
+      <x:c r="A24" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:1">
+      <x:c r="A25" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:1">
+      <x:c r="A26" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:1">
+      <x:c r="A27" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:1">
+      <x:c r="A28" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:1">
+      <x:c r="A29" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:1">
+      <x:c r="A30" s="0" t="s">
+        <x:v>95</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/docs/Пример спецификации.xlsx
+++ b/docs/Пример спецификации.xlsx
@@ -273,10 +273,10 @@
     <x:t>Ручной перенос строки — Alt+Enter внутри ячейки: в PDF текст перенесётся в этом месте (Обозначение, Наименование,</x:t>
   </x:si>
   <x:si>
-    <x:t>Примечание; на листе «Основная надпись» — Наименование и Организация). Без него длинный текст сжимается</x:t>
-  </x:si>
-  <x:si>
-    <x:t>до 80 % по ширине, а если не помещается и так — переносится по словам.</x:t>
+    <x:t>Примечание; на листе «Основная надпись» — Наименование). Без него длинный текст сужается по ширине</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(по умолчанию до 80 %, задаётся в утилите PDF), а если не помещается и так — переносится по словам.</x:t>
   </x:si>
   <x:si>
     <x:t>«Ед. изм.» выводится вместе с количеством (например, «2,5 м»); для штук оставьте пустым.</x:t>
@@ -285,10 +285,10 @@
     <x:t>Лист «Основная надпись» — данные для основной надписи (обозначение, наименование, подписи).</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">  «Шрифт наименования, мм» — высота шрифта наименования изделия в основной надписи (2,5; 3,5; 5; 7; 10).</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">  Не помещается — сжимается по ширине и переносится. Организация выводится шрифтом 10 одной строкой.</x:t>
+    <x:t xml:space="preserve">  «Шрифт наименования, мм» — высота шрифта наименования изделия для этого документа (2,5; 3,5; 5; 7; 10);</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">  пусто — из настроек утилиты PDF. Остальные размеры шрифтов и допустимое сужение текста задаются в утилите PDF.</x:t>
   </x:si>
   <x:si>
     <x:t>Лист «Изменения» — графы изменений основной надписи (ГОСТ 2.503), одна строка — одна запись, по порядку внесения:</x:t>
@@ -1609,9 +1609,7 @@
       <x:c r="A12" s="16" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="B12" s="17">
-        <x:v>5</x:v>
-      </x:c>
+      <x:c r="B12" s="17"/>
     </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
